--- a/astro-site/public/dl/kit-tareas-panaderia/03-hornos-coccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-panaderia/03-hornos-coccion.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hornos y Coccion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Hornos y Coccion'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -81,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -103,11 +105,55 @@
         <color rgb="00D4D0C8"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D4D0C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D4D0C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D4D0C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D4D0C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D4D0C8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D4D0C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D4D0C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D4D0C8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -128,10 +174,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -491,7 +549,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -556,6 +614,11 @@
           <t>HORNO DE PISO / SOLERA</t>
         </is>
       </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -711,6 +774,11 @@
           <t>HORNO ROTATIVO</t>
         </is>
       </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="9" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -838,6 +906,11 @@
           <t>TABLA DE TEMPERATURAS Y TIEMPOS</t>
         </is>
       </c>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1007,6 +1080,7 @@
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
@@ -1018,11 +1092,30 @@
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A4:F24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E4="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E12 E13 E14 E15 E16 E18 E19 E20 E21 E22 E23 E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>